--- a/output/pdf_financials_xlsx/PLLR.xlsx
+++ b/output/pdf_financials_xlsx/PLLR.xlsx
@@ -1936,13 +1936,13 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>0.389147</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>0.459752</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>0.419687</v>
       </c>
     </row>
     <row r="93">
@@ -3085,7 +3085,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E14" s="5" t="n">
         <v>0.389147</v>
       </c>

--- a/output/pdf_financials_xlsx/PLLR.xlsx
+++ b/output/pdf_financials_xlsx/PLLR.xlsx
@@ -609,13 +609,13 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.000691</v>
       </c>
       <c r="C12" s="3" t="n">
         <v>0</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.001253</v>
       </c>
     </row>
     <row r="13">
@@ -861,13 +861,13 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-1.615358</v>
+        <v>-1.616049</v>
       </c>
       <c r="C27" s="3" t="n">
         <v>-0.753807</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-1.735881</v>
+        <v>-1.737134</v>
       </c>
     </row>
     <row r="28">
@@ -893,13 +893,13 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-1.615358</v>
+        <v>-1.616049</v>
       </c>
       <c r="C29" s="3" t="n">
         <v>-0.753807</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-1.735881</v>
+        <v>-1.737134</v>
       </c>
     </row>
     <row r="30">
@@ -976,13 +976,13 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.058175</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.000364</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.0011</v>
       </c>
     </row>
     <row r="35">
@@ -1008,13 +1008,13 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.058175</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.000364</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.0011</v>
       </c>
     </row>
     <row r="37">
@@ -1200,13 +1200,13 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.058175</v>
+        <v>0</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.194232</v>
+        <v>0.193868</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.014344</v>
+        <v>0.013244</v>
       </c>
     </row>
     <row r="49">
@@ -2711,7 +2711,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">
@@ -5313,7 +5313,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E92" s="5" t="n">
@@ -5741,7 +5741,7 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E100" s="5" t="n">

--- a/output/pdf_financials_xlsx/PLLR.xlsx
+++ b/output/pdf_financials_xlsx/PLLR.xlsx
@@ -529,13 +529,13 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>0.060652</v>
+        <v>0.152652</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>0.108113</v>
+        <v>0.204113</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>0.001826</v>
+        <v>0.107826</v>
       </c>
     </row>
     <row r="8">
@@ -5187,7 +5187,11 @@
           <t>Flow-through shares issued for cash 1,818,182 163,636</t>
         </is>
       </c>
-      <c r="D82" t="inlineStr"/>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E82" s="5" t="n">
         <v>0.163636</v>
       </c>
@@ -5346,7 +5350,11 @@
           <t>Management and director fees 9</t>
         </is>
       </c>
-      <c r="D87" t="inlineStr"/>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E87" t="inlineStr">
         <is>
           <t>-</t>
@@ -5774,7 +5782,11 @@
           <t>Management and director fees 11</t>
         </is>
       </c>
-      <c r="D101" t="inlineStr"/>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E101" s="5" t="n">
         <v>0.092</v>
       </c>
